--- a/data/input/preparation/ai_results/quality_reports/adidas_disagreements_Leadership_context_human.xlsx
+++ b/data/input/preparation/ai_results/quality_reports/adidas_disagreements_Leadership_context_human.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
